--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/tlip.MS/RANDOMSEARCH_DETAILS_tlip.MS.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/tlip.MS/RANDOMSEARCH_DETAILS_tlip.MS.xlsx
@@ -413,9 +413,4084 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Compose</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID_Pretraitement</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Code_R_Pretraitement</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Meilleurs_Hyperparam_RF</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>RMSEC</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RMSECV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(1,3,5))</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9648</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.485</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.5843</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.5577</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9572000000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.5048</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.7291</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.6299</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1))</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9588</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.7857</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.8436</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.5283</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,700,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9748</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.5517</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.4421</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.7947</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,750,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9722</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.5463</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.4764</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.7758</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1000,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9469</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.6092</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.909</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.9873</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9534</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.6793</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.943</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.2107</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1200,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9550999999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.5228</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.7556</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.6938</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9526</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.681</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.9499</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.2158</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9477</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.6805</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.0255</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.2144</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9525</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.6794</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.9558</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.2108</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.6813</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.9551</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.2167</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9477</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.6792</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.0286</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.2104</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9523</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.679</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.9594</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.2097</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9523</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.6806</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.9541</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.2146</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9519</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.6788</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.9599</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.2092</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9282</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.5082</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.0478</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.6419</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9465</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.5004</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.8694</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.6138</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9612000000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.513</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.628</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.6589</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9536</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.5202</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.7705</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.6847</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9563</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.5282</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.6887</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.713</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9769</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.5151</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.3559</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.6667</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9510999999999999</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.5288</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.7799</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.7151</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9504</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.5277</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.8163</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.7111</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.5104</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.6186</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.6498</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9775</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.5087</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.3775</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.6437</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9286</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.4891</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.0484</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.5729</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9622000000000001</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.5101</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.6259</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3.6487</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.5214</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.7923</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3.6888</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9779</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.5222</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.3779</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3.6917</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9585</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.5144</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.6747</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.664</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9436</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.5299</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.916</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.7188</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9585</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.5696</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.7513</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.8556</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9494</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.5482</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.8924</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3.7825</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9595</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.5457</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.7466</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.7738</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9567</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.524</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.7422</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.6981</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9594</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.5003</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.7076</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3.6134</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9586</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.4887</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.6897</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.5712</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9802</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.477</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.3049</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3.5284</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9582000000000001</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.5692</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.7527</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3.8544</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9636</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.5514</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.6431</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3.7936</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9597</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.5471</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.7471</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.7788</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9812</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.5262</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1.3373</v>
+      </c>
+      <c r="H44" t="n">
+        <v>3.7058</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9577</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.5072</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.7804</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3.6385</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9617</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.4948</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.5973</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3.5934</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.4809</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.6367</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3.5428</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1400,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9817</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.5576</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1.394</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3.815</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(40,1300,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9593</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.5536</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1.7825</v>
+      </c>
+      <c r="H49" t="n">
+        <v>3.8012</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9804</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.5002</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.3516</v>
+      </c>
+      <c r="H50" t="n">
+        <v>3.613</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.5099</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.3421</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3.6478</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.9762999999999999</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.5106</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.3903</v>
+      </c>
+      <c r="H52" t="n">
+        <v>3.6507</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.4832</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2.0813</v>
+      </c>
+      <c r="H53" t="n">
+        <v>3.5513</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,21))</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.9463</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.4874</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1.8266</v>
+      </c>
+      <c r="H54" t="n">
+        <v>3.5667</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.9744</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.4756</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1.4443</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3.5231</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9735</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.4978</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1.4766</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3.6044</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,650,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.9505</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.5221</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1.7436</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3.6915</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,15))</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.9726</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.5434</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1.4691</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3.7658</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,21))</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.9722</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.5502</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1.4779</v>
+      </c>
+      <c r="H59" t="n">
+        <v>3.7894</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,25))</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.9724</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.5486</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.4692</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3.7837</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,31))</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.9725</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.5506</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1.464</v>
+      </c>
+      <c r="H61" t="n">
+        <v>3.7908</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.9454</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.5151</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1.8381</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3.6664</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>62</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.5043</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1.3817</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3.6278</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>63</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.9784</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.5123</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1.3479</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3.6566</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>64</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,31))</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.9439</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.5131</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1.9201</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3.6593</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>65</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.5145</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1.7784</v>
+      </c>
+      <c r="H66" t="n">
+        <v>3.6645</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>66</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,700,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.9202</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.5299</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2.2391</v>
+      </c>
+      <c r="H67" t="n">
+        <v>3.7189</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>67</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.9802999999999999</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.5366</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1.4061</v>
+      </c>
+      <c r="H68" t="n">
+        <v>3.7423</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>72</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,11)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.9318</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1.4898</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2.0306</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3.5753</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>73</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.9535</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1.4856</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1.7532</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3.5601</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>74</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.9592000000000001</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1.4755</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1.6372</v>
+      </c>
+      <c r="H71" t="n">
+        <v>3.5227</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>75</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.9318</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.491</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2.0396</v>
+      </c>
+      <c r="H72" t="n">
+        <v>3.5799</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>76</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.9461000000000001</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1.5747</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2.045</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3.873</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>77</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0.9562</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.5411</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1.7998</v>
+      </c>
+      <c r="H74" t="n">
+        <v>3.7579</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>78</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.8971</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1.6533</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="H75" t="n">
+        <v>4.1294</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>79</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0.8971</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.6533</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2.501</v>
+      </c>
+      <c r="H76" t="n">
+        <v>4.1294</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>80</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0.9751</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1.5402</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1.4582</v>
+      </c>
+      <c r="H77" t="n">
+        <v>3.7548</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>81</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1.5428</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1.4881</v>
+      </c>
+      <c r="H78" t="n">
+        <v>3.7638</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>82</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.9751</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1.5362</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1.449</v>
+      </c>
+      <c r="H79" t="n">
+        <v>3.741</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>83</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1.5428</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1.4868</v>
+      </c>
+      <c r="H80" t="n">
+        <v>3.7639</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>84</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.4958</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1.3484</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3.5974</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>85</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.9797</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1.3355</v>
+      </c>
+      <c r="H82" t="n">
+        <v>3.6123</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>86</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.9436</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1.6566</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1.9855</v>
+      </c>
+      <c r="H83" t="n">
+        <v>4.1397</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>87</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0.9447</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1.6543</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1.9771</v>
+      </c>
+      <c r="H84" t="n">
+        <v>4.1325</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>88</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.9434</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1.656</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1.9878</v>
+      </c>
+      <c r="H85" t="n">
+        <v>4.1376</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>89</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.9594</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1.4773</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1.6628</v>
+      </c>
+      <c r="H86" t="n">
+        <v>3.5294</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>90</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0.9627</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1.4754</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1.5926</v>
+      </c>
+      <c r="H87" t="n">
+        <v>3.5226</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>91</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0.9591</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1.5017</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1.6667</v>
+      </c>
+      <c r="H88" t="n">
+        <v>3.6187</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>92</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0.9564</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.4979</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1.7144</v>
+      </c>
+      <c r="H89" t="n">
+        <v>3.6048</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>93</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0.9597</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1.5475</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1.7472</v>
+      </c>
+      <c r="H90" t="n">
+        <v>3.7803</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>94</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0.9813</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1.526</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1.3365</v>
+      </c>
+      <c r="H91" t="n">
+        <v>3.7052</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>95</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0.9591</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1.5017</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1.6667</v>
+      </c>
+      <c r="H92" t="n">
+        <v>3.6187</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>96</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0.9813</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1.526</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1.3365</v>
+      </c>
+      <c r="H93" t="n">
+        <v>3.7052</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>97</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0.9588</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1.7857</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1.8436</v>
+      </c>
+      <c r="H94" t="n">
+        <v>4.5283</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>98</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0.8879</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1.6994</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2.5744</v>
+      </c>
+      <c r="H95" t="n">
+        <v>4.2725</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>99</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0.9707</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1.7767</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1.6063</v>
+      </c>
+      <c r="H96" t="n">
+        <v>4.5023</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>100</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0.8629</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1.7842</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2.7762</v>
+      </c>
+      <c r="H97" t="n">
+        <v>4.5241</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>101</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0.9326</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1.5026</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2.0355</v>
+      </c>
+      <c r="H98" t="n">
+        <v>3.6219</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>102</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0.9272</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.4901</v>
+      </c>
+      <c r="G99" t="n">
+        <v>2.072</v>
+      </c>
+      <c r="H99" t="n">
+        <v>3.5763</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>103</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0.9238</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.5037</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2.1003</v>
+      </c>
+      <c r="H100" t="n">
+        <v>3.6259</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>104</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0.9146</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1.4997</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2.2449</v>
+      </c>
+      <c r="H101" t="n">
+        <v>3.6112</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>105</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0.9212</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1.5042</v>
+      </c>
+      <c r="G102" t="n">
+        <v>2.1144</v>
+      </c>
+      <c r="H102" t="n">
+        <v>3.6277</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>106</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0.9346</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.5066</v>
+      </c>
+      <c r="G103" t="n">
+        <v>2.0186</v>
+      </c>
+      <c r="H103" t="n">
+        <v>3.6362</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>107</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0.9267</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.5057</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2.0818</v>
+      </c>
+      <c r="H104" t="n">
+        <v>3.6329</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>108</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0.9779</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1.4918</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1.354</v>
+      </c>
+      <c r="H105" t="n">
+        <v>3.5826</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>109</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0.9272</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G106" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="H106" t="n">
+        <v>3.6123</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>110</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0.9794</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.5036</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1.3308</v>
+      </c>
+      <c r="H107" t="n">
+        <v>3.6253</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>111</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0.9606</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.5995</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1.8873</v>
+      </c>
+      <c r="H108" t="n">
+        <v>3.9555</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>112</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0.9832</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1.5604</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1.4161</v>
+      </c>
+      <c r="H109" t="n">
+        <v>3.8245</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>113</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0.9808</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.5246</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1.4248</v>
+      </c>
+      <c r="H110" t="n">
+        <v>3.7003</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>114</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0.9818</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1.5119</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1.3588</v>
+      </c>
+      <c r="H111" t="n">
+        <v>3.6552</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>115</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0.9607</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.594</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1.8924</v>
+      </c>
+      <c r="H112" t="n">
+        <v>3.9375</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>116</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0.9294</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1.5531</v>
+      </c>
+      <c r="G113" t="n">
+        <v>2.2843</v>
+      </c>
+      <c r="H113" t="n">
+        <v>3.7994</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>117</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0.9806</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.5261</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1.4195</v>
+      </c>
+      <c r="H114" t="n">
+        <v>3.7055</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>118</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0.9814000000000001</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.5129</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1.3698</v>
+      </c>
+      <c r="H115" t="n">
+        <v>3.6589</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>119</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1.5285</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1.9068</v>
+      </c>
+      <c r="H116" t="n">
+        <v>3.7139</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>120</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0.9702</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.5108</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.5354</v>
+      </c>
+      <c r="H117" t="n">
+        <v>3.6513</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>121</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9779</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.4918</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.354</v>
+      </c>
+      <c r="H118" t="n">
+        <v>3.5826</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>122</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0.9294</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.5531</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2.2843</v>
+      </c>
+      <c r="H119" t="n">
+        <v>3.7994</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>123</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0.9083</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.6283</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="H120" t="n">
+        <v>4.0496</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>124</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0.9083</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.6283</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2.362</v>
+      </c>
+      <c r="H121" t="n">
+        <v>4.0496</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>125</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0.9774</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.4805</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1.336</v>
+      </c>
+      <c r="H122" t="n">
+        <v>3.5413</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>126</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0.9293</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.5533</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2.2853</v>
+      </c>
+      <c r="H123" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>127</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3'), list('sder',c(2,4,31))</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0.9625</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.5373</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1.7572</v>
+      </c>
+      <c r="H124" t="n">
+        <v>3.7446</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>172</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>list('snv',''),list('sder',c(1,3,9)),list('red',c(10,10,1))</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0.9575</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.4828</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1.6989</v>
+      </c>
+      <c r="H125" t="n">
+        <v>3.5499</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>173</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,4,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0.9815</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.6039</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1.4671</v>
+      </c>
+      <c r="H126" t="n">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>tlip.MS</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>174</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2,4,25))</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0.9574</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.5429</v>
+      </c>
+      <c r="G127" t="n">
+        <v>1.7178</v>
+      </c>
+      <c r="H127" t="n">
+        <v>3.7643</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/tlip.MS/RANDOMSEARCH_DETAILS_tlip.MS.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/tlip.MS/RANDOMSEARCH_DETAILS_tlip.MS.xlsx
@@ -474,20 +474,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9648</v>
+        <v>0.9811</v>
       </c>
       <c r="F2" t="n">
-        <v>1.485</v>
+        <v>0.4464</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5843</v>
+        <v>1.3663</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5577</v>
+        <v>3.7937</v>
       </c>
     </row>
     <row r="3">
@@ -506,20 +506,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9595</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5048</v>
+        <v>0.4536</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7291</v>
+        <v>1.6675</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6299</v>
+        <v>3.7691</v>
       </c>
     </row>
     <row r="4">
@@ -538,20 +538,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9588</v>
+        <v>0.9206</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7857</v>
+        <v>0.1844</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8436</v>
+        <v>2.4217</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5283</v>
+        <v>4.6046</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +570,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9748</v>
+        <v>0.871</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5517</v>
+        <v>0.4154</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4421</v>
+        <v>2.6079</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7947</v>
+        <v>3.8983</v>
       </c>
     </row>
     <row r="6">
@@ -602,20 +602,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.9722</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5463</v>
+        <v>0.3999</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4764</v>
+        <v>1.8504</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7758</v>
+        <v>3.9497</v>
       </c>
     </row>
     <row r="7">
@@ -634,20 +634,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9469</v>
+        <v>0.9547</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6092</v>
+        <v>0.3678</v>
       </c>
       <c r="G7" t="n">
-        <v>1.909</v>
+        <v>1.838</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9873</v>
+        <v>4.0542</v>
       </c>
     </row>
     <row r="8">
@@ -670,16 +670,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9534</v>
+        <v>0.9567</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6793</v>
+        <v>0.2448</v>
       </c>
       <c r="G8" t="n">
-        <v>1.943</v>
+        <v>1.974</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2107</v>
+        <v>4.4309</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.9587</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5228</v>
+        <v>0.4337</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7556</v>
+        <v>1.7029</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6938</v>
+        <v>3.8369</v>
       </c>
     </row>
     <row r="10">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9526</v>
+        <v>0.9583</v>
       </c>
       <c r="F10" t="n">
-        <v>1.681</v>
+        <v>0.2495</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9499</v>
+        <v>1.9627</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2158</v>
+        <v>4.4171</v>
       </c>
     </row>
     <row r="11">
@@ -762,20 +762,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9477</v>
+        <v>0.9579</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6805</v>
+        <v>0.2495</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0255</v>
+        <v>1.971</v>
       </c>
       <c r="H11" t="n">
-        <v>4.2144</v>
+        <v>4.4171</v>
       </c>
     </row>
     <row r="12">
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9525</v>
+        <v>0.9568</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6794</v>
+        <v>0.2522</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9558</v>
+        <v>1.9734</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2108</v>
+        <v>4.4093</v>
       </c>
     </row>
     <row r="13">
@@ -830,16 +830,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.952</v>
+        <v>0.957</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6813</v>
+        <v>0.2495</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9551</v>
+        <v>1.9858</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2167</v>
+        <v>4.4172</v>
       </c>
     </row>
     <row r="14">
@@ -858,20 +858,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9477</v>
+        <v>0.9581</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6792</v>
+        <v>0.2499</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0286</v>
+        <v>1.9665</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2104</v>
+        <v>4.4158</v>
       </c>
     </row>
     <row r="15">
@@ -894,16 +894,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9523</v>
+        <v>0.957</v>
       </c>
       <c r="F15" t="n">
-        <v>1.679</v>
+        <v>0.2518</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9594</v>
+        <v>1.9725</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2097</v>
+        <v>4.4103</v>
       </c>
     </row>
     <row r="16">
@@ -926,16 +926,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9523</v>
+        <v>0.9573</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6806</v>
+        <v>0.2557</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9541</v>
+        <v>1.9779</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2146</v>
+        <v>4.3988</v>
       </c>
     </row>
     <row r="17">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9519</v>
+        <v>0.9571</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6788</v>
+        <v>0.2505</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9599</v>
+        <v>1.9852</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2092</v>
+        <v>4.4142</v>
       </c>
     </row>
     <row r="18">
@@ -986,20 +986,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9282</v>
+        <v>0.9394</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5082</v>
+        <v>0.4403</v>
       </c>
       <c r="G18" t="n">
-        <v>2.0478</v>
+        <v>1.9766</v>
       </c>
       <c r="H18" t="n">
-        <v>3.6419</v>
+        <v>3.8146</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9465</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5004</v>
+        <v>0.4306</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8694</v>
+        <v>1.6742</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6138</v>
+        <v>3.8474</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9612000000000001</v>
+        <v>0.9473</v>
       </c>
       <c r="F20" t="n">
-        <v>1.513</v>
+        <v>0.4371</v>
       </c>
       <c r="G20" t="n">
-        <v>1.628</v>
+        <v>1.8416</v>
       </c>
       <c r="H20" t="n">
-        <v>3.6589</v>
+        <v>3.8255</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9536</v>
+        <v>0.9748</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5202</v>
+        <v>0.4239</v>
       </c>
       <c r="G21" t="n">
-        <v>1.7705</v>
+        <v>1.4074</v>
       </c>
       <c r="H21" t="n">
-        <v>3.6847</v>
+        <v>3.8701</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9563</v>
+        <v>0.9318</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5282</v>
+        <v>0.4198</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6887</v>
+        <v>2.0639</v>
       </c>
       <c r="H22" t="n">
-        <v>3.713</v>
+        <v>3.8838</v>
       </c>
     </row>
     <row r="23">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9769</v>
+        <v>0.9764</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5151</v>
+        <v>0.4321</v>
       </c>
       <c r="G23" t="n">
-        <v>1.3559</v>
+        <v>1.4185</v>
       </c>
       <c r="H23" t="n">
-        <v>3.6667</v>
+        <v>3.8425</v>
       </c>
     </row>
     <row r="24">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.9762</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5288</v>
+        <v>0.4309</v>
       </c>
       <c r="G24" t="n">
-        <v>1.7799</v>
+        <v>1.4189</v>
       </c>
       <c r="H24" t="n">
-        <v>3.7151</v>
+        <v>3.8465</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9504</v>
+        <v>0.9765</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5277</v>
+        <v>0.4367</v>
       </c>
       <c r="G25" t="n">
-        <v>1.8163</v>
+        <v>1.3714</v>
       </c>
       <c r="H25" t="n">
-        <v>3.7111</v>
+        <v>3.8267</v>
       </c>
     </row>
     <row r="26">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.963</v>
+        <v>0.9553</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5104</v>
+        <v>0.4314</v>
       </c>
       <c r="G26" t="n">
-        <v>1.6186</v>
+        <v>1.7796</v>
       </c>
       <c r="H26" t="n">
-        <v>3.6498</v>
+        <v>3.8446</v>
       </c>
     </row>
     <row r="27">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9775</v>
+        <v>0.9611</v>
       </c>
       <c r="F27" t="n">
-        <v>1.5087</v>
+        <v>0.4315</v>
       </c>
       <c r="G27" t="n">
-        <v>1.3775</v>
+        <v>1.6562</v>
       </c>
       <c r="H27" t="n">
-        <v>3.6437</v>
+        <v>3.8445</v>
       </c>
     </row>
     <row r="28">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9286</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>1.4891</v>
+        <v>0.4392</v>
       </c>
       <c r="G28" t="n">
-        <v>2.0484</v>
+        <v>1.8238</v>
       </c>
       <c r="H28" t="n">
-        <v>3.5729</v>
+        <v>3.8184</v>
       </c>
     </row>
     <row r="29">
@@ -1338,20 +1338,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9483</v>
       </c>
       <c r="F29" t="n">
-        <v>1.5101</v>
+        <v>0.4303</v>
       </c>
       <c r="G29" t="n">
-        <v>1.6259</v>
+        <v>1.8082</v>
       </c>
       <c r="H29" t="n">
-        <v>3.6487</v>
+        <v>3.8484</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.951</v>
+        <v>0.9375</v>
       </c>
       <c r="F30" t="n">
-        <v>1.5214</v>
+        <v>0.4332</v>
       </c>
       <c r="G30" t="n">
-        <v>1.7923</v>
+        <v>2.0245</v>
       </c>
       <c r="H30" t="n">
-        <v>3.6888</v>
+        <v>3.8386</v>
       </c>
     </row>
     <row r="31">
@@ -1402,20 +1402,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9779</v>
+        <v>0.9452</v>
       </c>
       <c r="F31" t="n">
-        <v>1.5222</v>
+        <v>0.4263</v>
       </c>
       <c r="G31" t="n">
-        <v>1.3779</v>
+        <v>1.8673</v>
       </c>
       <c r="H31" t="n">
-        <v>3.6917</v>
+        <v>3.8618</v>
       </c>
     </row>
     <row r="32">
@@ -1434,20 +1434,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9585</v>
+        <v>0.9567</v>
       </c>
       <c r="F32" t="n">
-        <v>1.5144</v>
+        <v>0.4203</v>
       </c>
       <c r="G32" t="n">
-        <v>1.6747</v>
+        <v>1.7183</v>
       </c>
       <c r="H32" t="n">
-        <v>3.664</v>
+        <v>3.8819</v>
       </c>
     </row>
     <row r="33">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9436</v>
+        <v>0.9598</v>
       </c>
       <c r="F33" t="n">
-        <v>1.5299</v>
+        <v>0.4282</v>
       </c>
       <c r="G33" t="n">
-        <v>1.916</v>
+        <v>1.6902</v>
       </c>
       <c r="H33" t="n">
-        <v>3.7188</v>
+        <v>3.8554</v>
       </c>
     </row>
     <row r="34">
@@ -1498,20 +1498,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9585</v>
+        <v>0.9292</v>
       </c>
       <c r="F34" t="n">
-        <v>1.5696</v>
+        <v>0.3704</v>
       </c>
       <c r="G34" t="n">
-        <v>1.7513</v>
+        <v>2.1622</v>
       </c>
       <c r="H34" t="n">
-        <v>3.8556</v>
+        <v>4.0456</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9494</v>
+        <v>0.9637</v>
       </c>
       <c r="F35" t="n">
-        <v>1.5482</v>
+        <v>0.3904</v>
       </c>
       <c r="G35" t="n">
-        <v>1.8924</v>
+        <v>1.667</v>
       </c>
       <c r="H35" t="n">
-        <v>3.7825</v>
+        <v>3.981</v>
       </c>
     </row>
     <row r="36">
@@ -1562,20 +1562,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9595</v>
+        <v>0.9213</v>
       </c>
       <c r="F36" t="n">
-        <v>1.5457</v>
+        <v>0.4107</v>
       </c>
       <c r="G36" t="n">
-        <v>1.7466</v>
+        <v>2.2822</v>
       </c>
       <c r="H36" t="n">
-        <v>3.7738</v>
+        <v>3.9142</v>
       </c>
     </row>
     <row r="37">
@@ -1594,20 +1594,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9567</v>
+        <v>0.9591</v>
       </c>
       <c r="F37" t="n">
-        <v>1.524</v>
+        <v>0.4203</v>
       </c>
       <c r="G37" t="n">
-        <v>1.7422</v>
+        <v>1.6782</v>
       </c>
       <c r="H37" t="n">
-        <v>3.6981</v>
+        <v>3.8821</v>
       </c>
     </row>
     <row r="38">
@@ -1630,16 +1630,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9594</v>
+        <v>0.9599</v>
       </c>
       <c r="F38" t="n">
-        <v>1.5003</v>
+        <v>0.448</v>
       </c>
       <c r="G38" t="n">
-        <v>1.7076</v>
+        <v>1.7184</v>
       </c>
       <c r="H38" t="n">
-        <v>3.6134</v>
+        <v>3.7883</v>
       </c>
     </row>
     <row r="39">
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9586</v>
+        <v>0.9605</v>
       </c>
       <c r="F39" t="n">
-        <v>1.4887</v>
+        <v>0.4583</v>
       </c>
       <c r="G39" t="n">
-        <v>1.6897</v>
+        <v>1.6578</v>
       </c>
       <c r="H39" t="n">
-        <v>3.5712</v>
+        <v>3.7526</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9802</v>
+        <v>0.9594</v>
       </c>
       <c r="F40" t="n">
-        <v>1.477</v>
+        <v>0.4579</v>
       </c>
       <c r="G40" t="n">
-        <v>1.3049</v>
+        <v>1.6976</v>
       </c>
       <c r="H40" t="n">
-        <v>3.5284</v>
+        <v>3.754</v>
       </c>
     </row>
     <row r="41">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.9291</v>
       </c>
       <c r="F41" t="n">
-        <v>1.5692</v>
+        <v>0.3685</v>
       </c>
       <c r="G41" t="n">
-        <v>1.7527</v>
+        <v>2.1619</v>
       </c>
       <c r="H41" t="n">
-        <v>3.8544</v>
+        <v>4.0519</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9636</v>
+        <v>0.9272</v>
       </c>
       <c r="F42" t="n">
-        <v>1.5514</v>
+        <v>0.3912</v>
       </c>
       <c r="G42" t="n">
-        <v>1.6431</v>
+        <v>2.1448</v>
       </c>
       <c r="H42" t="n">
-        <v>3.7936</v>
+        <v>3.9782</v>
       </c>
     </row>
     <row r="43">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9597</v>
+        <v>0.9595</v>
       </c>
       <c r="F43" t="n">
-        <v>1.5471</v>
+        <v>0.4086</v>
       </c>
       <c r="G43" t="n">
-        <v>1.7471</v>
+        <v>1.7202</v>
       </c>
       <c r="H43" t="n">
-        <v>3.7788</v>
+        <v>3.921</v>
       </c>
     </row>
     <row r="44">
@@ -1818,20 +1818,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9812</v>
+        <v>0.9643</v>
       </c>
       <c r="F44" t="n">
-        <v>1.5262</v>
+        <v>0.418</v>
       </c>
       <c r="G44" t="n">
-        <v>1.3373</v>
+        <v>1.6215</v>
       </c>
       <c r="H44" t="n">
-        <v>3.7058</v>
+        <v>3.8897</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9577</v>
+        <v>0.9603</v>
       </c>
       <c r="F45" t="n">
-        <v>1.5072</v>
+        <v>0.4488</v>
       </c>
       <c r="G45" t="n">
-        <v>1.7804</v>
+        <v>1.7197</v>
       </c>
       <c r="H45" t="n">
-        <v>3.6385</v>
+        <v>3.7854</v>
       </c>
     </row>
     <row r="46">
@@ -1882,20 +1882,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9617</v>
+        <v>0.9616</v>
       </c>
       <c r="F46" t="n">
-        <v>1.4948</v>
+        <v>0.4521</v>
       </c>
       <c r="G46" t="n">
-        <v>1.5973</v>
+        <v>1.6518</v>
       </c>
       <c r="H46" t="n">
-        <v>3.5934</v>
+        <v>3.7742</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.959</v>
+        <v>0.9759</v>
       </c>
       <c r="F47" t="n">
-        <v>1.4809</v>
+        <v>0.4589</v>
       </c>
       <c r="G47" t="n">
-        <v>1.6367</v>
+        <v>1.4223</v>
       </c>
       <c r="H47" t="n">
-        <v>3.5428</v>
+        <v>3.7506</v>
       </c>
     </row>
     <row r="48">
@@ -1946,20 +1946,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9817</v>
+        <v>0.9638</v>
       </c>
       <c r="F48" t="n">
-        <v>1.5576</v>
+        <v>0.4094</v>
       </c>
       <c r="G48" t="n">
-        <v>1.394</v>
+        <v>1.6479</v>
       </c>
       <c r="H48" t="n">
-        <v>3.815</v>
+        <v>3.9183</v>
       </c>
     </row>
     <row r="49">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9593</v>
+        <v>0.9563</v>
       </c>
       <c r="F49" t="n">
-        <v>1.5536</v>
+        <v>0.4116</v>
       </c>
       <c r="G49" t="n">
-        <v>1.7825</v>
+        <v>1.8146</v>
       </c>
       <c r="H49" t="n">
-        <v>3.8012</v>
+        <v>3.9112</v>
       </c>
     </row>
     <row r="50">
@@ -2010,20 +2010,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9804</v>
+        <v>0.972</v>
       </c>
       <c r="F50" t="n">
-        <v>1.5002</v>
+        <v>0.4467</v>
       </c>
       <c r="G50" t="n">
-        <v>1.3516</v>
+        <v>1.4958</v>
       </c>
       <c r="H50" t="n">
-        <v>3.613</v>
+        <v>3.7927</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.9799</v>
+        <v>0.9771</v>
       </c>
       <c r="F51" t="n">
-        <v>1.5099</v>
+        <v>0.4292</v>
       </c>
       <c r="G51" t="n">
-        <v>1.3421</v>
+        <v>1.3801</v>
       </c>
       <c r="H51" t="n">
-        <v>3.6478</v>
+        <v>3.8523</v>
       </c>
     </row>
     <row r="52">
@@ -2074,20 +2074,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9702</v>
       </c>
       <c r="F52" t="n">
-        <v>1.5106</v>
+        <v>0.4291</v>
       </c>
       <c r="G52" t="n">
-        <v>1.3903</v>
+        <v>1.531</v>
       </c>
       <c r="H52" t="n">
-        <v>3.6507</v>
+        <v>3.8526</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.9137</v>
       </c>
       <c r="F53" t="n">
-        <v>1.4832</v>
+        <v>0.453</v>
       </c>
       <c r="G53" t="n">
-        <v>2.0813</v>
+        <v>2.2017</v>
       </c>
       <c r="H53" t="n">
-        <v>3.5513</v>
+        <v>3.7709</v>
       </c>
     </row>
     <row r="54">
@@ -2138,20 +2138,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.9463</v>
+        <v>0.913</v>
       </c>
       <c r="F54" t="n">
-        <v>1.4874</v>
+        <v>0.4626</v>
       </c>
       <c r="G54" t="n">
-        <v>1.8266</v>
+        <v>2.1975</v>
       </c>
       <c r="H54" t="n">
-        <v>3.5667</v>
+        <v>3.7379</v>
       </c>
     </row>
     <row r="55">
@@ -2174,16 +2174,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.9744</v>
+        <v>0.9739</v>
       </c>
       <c r="F55" t="n">
-        <v>1.4756</v>
+        <v>0.4705</v>
       </c>
       <c r="G55" t="n">
-        <v>1.4443</v>
+        <v>1.4828</v>
       </c>
       <c r="H55" t="n">
-        <v>3.5231</v>
+        <v>3.7102</v>
       </c>
     </row>
     <row r="56">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9735</v>
+        <v>0.9517</v>
       </c>
       <c r="F56" t="n">
-        <v>1.4978</v>
+        <v>0.4321</v>
       </c>
       <c r="G56" t="n">
-        <v>1.4766</v>
+        <v>1.7928</v>
       </c>
       <c r="H56" t="n">
-        <v>3.6044</v>
+        <v>3.8423</v>
       </c>
     </row>
     <row r="57">
@@ -2234,20 +2234,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9505</v>
+        <v>0.9137</v>
       </c>
       <c r="F57" t="n">
-        <v>1.5221</v>
+        <v>0.4116</v>
       </c>
       <c r="G57" t="n">
-        <v>1.7436</v>
+        <v>2.1971</v>
       </c>
       <c r="H57" t="n">
-        <v>3.6915</v>
+        <v>3.911</v>
       </c>
     </row>
     <row r="58">
@@ -2266,20 +2266,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.9726</v>
+        <v>0.9439</v>
       </c>
       <c r="F58" t="n">
-        <v>1.5434</v>
+        <v>0.3996</v>
       </c>
       <c r="G58" t="n">
-        <v>1.4691</v>
+        <v>1.8624</v>
       </c>
       <c r="H58" t="n">
-        <v>3.7658</v>
+        <v>3.9507</v>
       </c>
     </row>
     <row r="59">
@@ -2298,20 +2298,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.9722</v>
+        <v>0.9442</v>
       </c>
       <c r="F59" t="n">
-        <v>1.5502</v>
+        <v>0.3967</v>
       </c>
       <c r="G59" t="n">
-        <v>1.4779</v>
+        <v>1.8585</v>
       </c>
       <c r="H59" t="n">
-        <v>3.7894</v>
+        <v>3.9603</v>
       </c>
     </row>
     <row r="60">
@@ -2330,20 +2330,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.9724</v>
+        <v>0.9284</v>
       </c>
       <c r="F60" t="n">
-        <v>1.5486</v>
+        <v>0.3952</v>
       </c>
       <c r="G60" t="n">
-        <v>1.4692</v>
+        <v>2.0447</v>
       </c>
       <c r="H60" t="n">
-        <v>3.7837</v>
+        <v>3.9653</v>
       </c>
     </row>
     <row r="61">
@@ -2362,20 +2362,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.9725</v>
+        <v>0.9455</v>
       </c>
       <c r="F61" t="n">
-        <v>1.5506</v>
+        <v>0.3968</v>
       </c>
       <c r="G61" t="n">
-        <v>1.464</v>
+        <v>1.8461</v>
       </c>
       <c r="H61" t="n">
-        <v>3.7908</v>
+        <v>3.9601</v>
       </c>
     </row>
     <row r="62">
@@ -2394,20 +2394,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.9454</v>
+        <v>0.9767</v>
       </c>
       <c r="F62" t="n">
-        <v>1.5151</v>
+        <v>0.4577</v>
       </c>
       <c r="G62" t="n">
-        <v>1.8381</v>
+        <v>1.4019</v>
       </c>
       <c r="H62" t="n">
-        <v>3.6664</v>
+        <v>3.7549</v>
       </c>
     </row>
     <row r="63">
@@ -2426,20 +2426,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9764</v>
       </c>
       <c r="F63" t="n">
-        <v>1.5043</v>
+        <v>0.455</v>
       </c>
       <c r="G63" t="n">
-        <v>1.3817</v>
+        <v>1.3934</v>
       </c>
       <c r="H63" t="n">
-        <v>3.6278</v>
+        <v>3.7642</v>
       </c>
     </row>
     <row r="64">
@@ -2458,20 +2458,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.9784</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>1.5123</v>
+        <v>0.4471</v>
       </c>
       <c r="G64" t="n">
-        <v>1.3479</v>
+        <v>1.5636</v>
       </c>
       <c r="H64" t="n">
-        <v>3.6566</v>
+        <v>3.7912</v>
       </c>
     </row>
     <row r="65">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.9439</v>
+        <v>0.9375</v>
       </c>
       <c r="F65" t="n">
-        <v>1.5131</v>
+        <v>0.4396</v>
       </c>
       <c r="G65" t="n">
-        <v>1.9201</v>
+        <v>1.9966</v>
       </c>
       <c r="H65" t="n">
-        <v>3.6593</v>
+        <v>3.8168</v>
       </c>
     </row>
     <row r="66">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9555</v>
+        <v>0.9761</v>
       </c>
       <c r="F66" t="n">
-        <v>1.5145</v>
+        <v>0.4118</v>
       </c>
       <c r="G66" t="n">
-        <v>1.7784</v>
+        <v>1.4103</v>
       </c>
       <c r="H66" t="n">
-        <v>3.6645</v>
+        <v>3.9105</v>
       </c>
     </row>
     <row r="67">
@@ -2554,20 +2554,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9202</v>
+        <v>0.9782</v>
       </c>
       <c r="F67" t="n">
-        <v>1.5299</v>
+        <v>0.4015</v>
       </c>
       <c r="G67" t="n">
-        <v>2.2391</v>
+        <v>1.437</v>
       </c>
       <c r="H67" t="n">
-        <v>3.7189</v>
+        <v>3.9444</v>
       </c>
     </row>
     <row r="68">
@@ -2586,20 +2586,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F68" t="n">
-        <v>1.5366</v>
+        <v>0.4173</v>
       </c>
       <c r="G68" t="n">
-        <v>1.4061</v>
+        <v>1.4244</v>
       </c>
       <c r="H68" t="n">
-        <v>3.7423</v>
+        <v>3.8922</v>
       </c>
     </row>
     <row r="69">
@@ -2618,20 +2618,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9318</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="F69" t="n">
-        <v>1.4898</v>
+        <v>0.456</v>
       </c>
       <c r="G69" t="n">
-        <v>2.0306</v>
+        <v>1.7813</v>
       </c>
       <c r="H69" t="n">
-        <v>3.5753</v>
+        <v>3.7606</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9535</v>
+        <v>0.9581</v>
       </c>
       <c r="F70" t="n">
-        <v>1.4856</v>
+        <v>0.4411</v>
       </c>
       <c r="G70" t="n">
-        <v>1.7532</v>
+        <v>1.6647</v>
       </c>
       <c r="H70" t="n">
-        <v>3.5601</v>
+        <v>3.8118</v>
       </c>
     </row>
     <row r="71">
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>1.4755</v>
+        <v>0.4462</v>
       </c>
       <c r="G71" t="n">
-        <v>1.6372</v>
+        <v>1.7609</v>
       </c>
       <c r="H71" t="n">
-        <v>3.5227</v>
+        <v>3.7943</v>
       </c>
     </row>
     <row r="72">
@@ -2714,20 +2714,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9318</v>
+        <v>0.9208</v>
       </c>
       <c r="F72" t="n">
-        <v>1.491</v>
+        <v>0.4456</v>
       </c>
       <c r="G72" t="n">
-        <v>2.0396</v>
+        <v>2.1357</v>
       </c>
       <c r="H72" t="n">
-        <v>3.5799</v>
+        <v>3.7963</v>
       </c>
     </row>
     <row r="73">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.965</v>
       </c>
       <c r="F73" t="n">
-        <v>1.5747</v>
+        <v>0.3597</v>
       </c>
       <c r="G73" t="n">
-        <v>2.045</v>
+        <v>1.7684</v>
       </c>
       <c r="H73" t="n">
-        <v>3.873</v>
+        <v>4.0798</v>
       </c>
     </row>
     <row r="74">
@@ -2782,16 +2782,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9562</v>
+        <v>0.956</v>
       </c>
       <c r="F74" t="n">
-        <v>1.5411</v>
+        <v>0.3794</v>
       </c>
       <c r="G74" t="n">
-        <v>1.7998</v>
+        <v>1.8304</v>
       </c>
       <c r="H74" t="n">
-        <v>3.7579</v>
+        <v>4.0168</v>
       </c>
     </row>
     <row r="75">
@@ -2810,20 +2810,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.8971</v>
+        <v>0.9499</v>
       </c>
       <c r="F75" t="n">
-        <v>1.6533</v>
+        <v>0.2975</v>
       </c>
       <c r="G75" t="n">
-        <v>2.501</v>
+        <v>1.9306</v>
       </c>
       <c r="H75" t="n">
-        <v>4.1294</v>
+        <v>4.2734</v>
       </c>
     </row>
     <row r="76">
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.8971</v>
+        <v>0.9499</v>
       </c>
       <c r="F76" t="n">
-        <v>1.6533</v>
+        <v>0.2975</v>
       </c>
       <c r="G76" t="n">
-        <v>2.501</v>
+        <v>1.9306</v>
       </c>
       <c r="H76" t="n">
-        <v>4.1294</v>
+        <v>4.2734</v>
       </c>
     </row>
     <row r="77">
@@ -2874,20 +2874,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.9751</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="F77" t="n">
-        <v>1.5402</v>
+        <v>0.3848</v>
       </c>
       <c r="G77" t="n">
-        <v>1.4582</v>
+        <v>2.1441</v>
       </c>
       <c r="H77" t="n">
-        <v>3.7548</v>
+        <v>3.9992</v>
       </c>
     </row>
     <row r="78">
@@ -2906,20 +2906,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.973</v>
+        <v>0.9253</v>
       </c>
       <c r="F78" t="n">
-        <v>1.5428</v>
+        <v>0.3878</v>
       </c>
       <c r="G78" t="n">
-        <v>1.4881</v>
+        <v>2.1461</v>
       </c>
       <c r="H78" t="n">
-        <v>3.7638</v>
+        <v>3.9893</v>
       </c>
     </row>
     <row r="79">
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.9751</v>
+        <v>0.928</v>
       </c>
       <c r="F79" t="n">
-        <v>1.5362</v>
+        <v>0.3858</v>
       </c>
       <c r="G79" t="n">
-        <v>1.449</v>
+        <v>2.122</v>
       </c>
       <c r="H79" t="n">
-        <v>3.741</v>
+        <v>3.996</v>
       </c>
     </row>
     <row r="80">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.973</v>
+        <v>0.9253</v>
       </c>
       <c r="F80" t="n">
-        <v>1.5428</v>
+        <v>0.3884</v>
       </c>
       <c r="G80" t="n">
-        <v>1.4868</v>
+        <v>2.1467</v>
       </c>
       <c r="H80" t="n">
-        <v>3.7639</v>
+        <v>3.9875</v>
       </c>
     </row>
     <row r="81">
@@ -3002,20 +3002,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.979</v>
+        <v>0.9416</v>
       </c>
       <c r="F81" t="n">
-        <v>1.4958</v>
+        <v>0.4651</v>
       </c>
       <c r="G81" t="n">
-        <v>1.3484</v>
+        <v>1.865</v>
       </c>
       <c r="H81" t="n">
-        <v>3.5974</v>
+        <v>3.7292</v>
       </c>
     </row>
     <row r="82">
@@ -3034,20 +3034,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.9797</v>
+        <v>0.9135</v>
       </c>
       <c r="F82" t="n">
-        <v>1.5</v>
+        <v>0.4499</v>
       </c>
       <c r="G82" t="n">
-        <v>1.3355</v>
+        <v>2.2095</v>
       </c>
       <c r="H82" t="n">
-        <v>3.6123</v>
+        <v>3.7816</v>
       </c>
     </row>
     <row r="83">
@@ -3066,20 +3066,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9436</v>
+        <v>0.8925</v>
       </c>
       <c r="F83" t="n">
-        <v>1.6566</v>
+        <v>0.2945</v>
       </c>
       <c r="G83" t="n">
-        <v>1.9855</v>
+        <v>2.6365</v>
       </c>
       <c r="H83" t="n">
-        <v>4.1397</v>
+        <v>4.2827</v>
       </c>
     </row>
     <row r="84">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9447</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="F84" t="n">
-        <v>1.6543</v>
+        <v>0.2961</v>
       </c>
       <c r="G84" t="n">
-        <v>1.9771</v>
+        <v>1.913</v>
       </c>
       <c r="H84" t="n">
-        <v>4.1325</v>
+        <v>4.2778</v>
       </c>
     </row>
     <row r="85">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9434</v>
+        <v>0.8925</v>
       </c>
       <c r="F85" t="n">
-        <v>1.656</v>
+        <v>0.2954</v>
       </c>
       <c r="G85" t="n">
-        <v>1.9878</v>
+        <v>2.6372</v>
       </c>
       <c r="H85" t="n">
-        <v>4.1376</v>
+        <v>4.2798</v>
       </c>
     </row>
     <row r="86">
@@ -3162,20 +3162,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9594</v>
+        <v>0.9578</v>
       </c>
       <c r="F86" t="n">
-        <v>1.4773</v>
+        <v>0.4484</v>
       </c>
       <c r="G86" t="n">
-        <v>1.6628</v>
+        <v>1.7417</v>
       </c>
       <c r="H86" t="n">
-        <v>3.5294</v>
+        <v>3.7868</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9627</v>
+        <v>0.9577</v>
       </c>
       <c r="F87" t="n">
-        <v>1.4754</v>
+        <v>0.443</v>
       </c>
       <c r="G87" t="n">
-        <v>1.5926</v>
+        <v>1.7343</v>
       </c>
       <c r="H87" t="n">
-        <v>3.5226</v>
+        <v>3.8053</v>
       </c>
     </row>
     <row r="88">
@@ -3226,20 +3226,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9591</v>
+        <v>0.9594</v>
       </c>
       <c r="F88" t="n">
-        <v>1.5017</v>
+        <v>0.4483</v>
       </c>
       <c r="G88" t="n">
-        <v>1.6667</v>
+        <v>1.7144</v>
       </c>
       <c r="H88" t="n">
-        <v>3.6187</v>
+        <v>3.7873</v>
       </c>
     </row>
     <row r="89">
@@ -3262,16 +3262,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9564</v>
+        <v>0.9557</v>
       </c>
       <c r="F89" t="n">
-        <v>1.4979</v>
+        <v>0.4375</v>
       </c>
       <c r="G89" t="n">
-        <v>1.7144</v>
+        <v>1.7519</v>
       </c>
       <c r="H89" t="n">
-        <v>3.6048</v>
+        <v>3.824</v>
       </c>
     </row>
     <row r="90">
@@ -3290,20 +3290,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E90" t="n">
         <v>0.9597</v>
       </c>
       <c r="F90" t="n">
-        <v>1.5475</v>
+        <v>0.4085</v>
       </c>
       <c r="G90" t="n">
-        <v>1.7472</v>
+        <v>1.7199</v>
       </c>
       <c r="H90" t="n">
-        <v>3.7803</v>
+        <v>3.9214</v>
       </c>
     </row>
     <row r="91">
@@ -3322,20 +3322,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9813</v>
+        <v>0.9748</v>
       </c>
       <c r="F91" t="n">
-        <v>1.526</v>
+        <v>0.4178</v>
       </c>
       <c r="G91" t="n">
-        <v>1.3365</v>
+        <v>1.5367</v>
       </c>
       <c r="H91" t="n">
-        <v>3.7052</v>
+        <v>3.8904</v>
       </c>
     </row>
     <row r="92">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9591</v>
+        <v>0.9594</v>
       </c>
       <c r="F92" t="n">
-        <v>1.5017</v>
+        <v>0.4483</v>
       </c>
       <c r="G92" t="n">
-        <v>1.6667</v>
+        <v>1.7144</v>
       </c>
       <c r="H92" t="n">
-        <v>3.6187</v>
+        <v>3.7873</v>
       </c>
     </row>
     <row r="93">
@@ -3386,20 +3386,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9813</v>
+        <v>0.9748</v>
       </c>
       <c r="F93" t="n">
-        <v>1.526</v>
+        <v>0.4178</v>
       </c>
       <c r="G93" t="n">
-        <v>1.3365</v>
+        <v>1.5367</v>
       </c>
       <c r="H93" t="n">
-        <v>3.7052</v>
+        <v>3.8904</v>
       </c>
     </row>
     <row r="94">
@@ -3418,20 +3418,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9588</v>
+        <v>0.9206</v>
       </c>
       <c r="F94" t="n">
-        <v>1.7857</v>
+        <v>0.1844</v>
       </c>
       <c r="G94" t="n">
-        <v>1.8436</v>
+        <v>2.4217</v>
       </c>
       <c r="H94" t="n">
-        <v>4.5283</v>
+        <v>4.6046</v>
       </c>
     </row>
     <row r="95">
@@ -3450,20 +3450,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.8879</v>
+        <v>0.833</v>
       </c>
       <c r="F95" t="n">
-        <v>1.6994</v>
+        <v>0.1881</v>
       </c>
       <c r="G95" t="n">
-        <v>2.5744</v>
+        <v>3.0753</v>
       </c>
       <c r="H95" t="n">
-        <v>4.2725</v>
+        <v>4.5943</v>
       </c>
     </row>
     <row r="96">
@@ -3482,20 +3482,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9707</v>
+        <v>0.9253</v>
       </c>
       <c r="F96" t="n">
-        <v>1.7767</v>
+        <v>0.1927</v>
       </c>
       <c r="G96" t="n">
-        <v>1.6063</v>
+        <v>2.2789</v>
       </c>
       <c r="H96" t="n">
-        <v>4.5023</v>
+        <v>4.5813</v>
       </c>
     </row>
     <row r="97">
@@ -3514,20 +3514,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.8629</v>
+        <v>0.9596</v>
       </c>
       <c r="F97" t="n">
-        <v>1.7842</v>
+        <v>0.1919</v>
       </c>
       <c r="G97" t="n">
-        <v>2.7762</v>
+        <v>1.8424</v>
       </c>
       <c r="H97" t="n">
-        <v>4.5241</v>
+        <v>4.5835</v>
       </c>
     </row>
     <row r="98">
@@ -3546,20 +3546,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9326</v>
+        <v>0.953</v>
       </c>
       <c r="F98" t="n">
-        <v>1.5026</v>
+        <v>0.4326</v>
       </c>
       <c r="G98" t="n">
-        <v>2.0355</v>
+        <v>1.8395</v>
       </c>
       <c r="H98" t="n">
-        <v>3.6219</v>
+        <v>3.8406</v>
       </c>
     </row>
     <row r="99">
@@ -3578,20 +3578,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9272</v>
+        <v>0.9536</v>
       </c>
       <c r="F99" t="n">
-        <v>1.4901</v>
+        <v>0.4604</v>
       </c>
       <c r="G99" t="n">
-        <v>2.072</v>
+        <v>1.8137</v>
       </c>
       <c r="H99" t="n">
-        <v>3.5763</v>
+        <v>3.7453</v>
       </c>
     </row>
     <row r="100">
@@ -3610,20 +3610,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9238</v>
+        <v>0.9544</v>
       </c>
       <c r="F100" t="n">
-        <v>1.5037</v>
+        <v>0.4502</v>
       </c>
       <c r="G100" t="n">
-        <v>2.1003</v>
+        <v>1.7133</v>
       </c>
       <c r="H100" t="n">
-        <v>3.6259</v>
+        <v>3.7807</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9146</v>
+        <v>0.9475</v>
       </c>
       <c r="F101" t="n">
-        <v>1.4997</v>
+        <v>0.4557</v>
       </c>
       <c r="G101" t="n">
-        <v>2.2449</v>
+        <v>1.8475</v>
       </c>
       <c r="H101" t="n">
-        <v>3.6112</v>
+        <v>3.7617</v>
       </c>
     </row>
     <row r="102">
@@ -3674,20 +3674,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9212</v>
+        <v>0.9767</v>
       </c>
       <c r="F102" t="n">
-        <v>1.5042</v>
+        <v>0.4458</v>
       </c>
       <c r="G102" t="n">
-        <v>2.1144</v>
+        <v>1.3705</v>
       </c>
       <c r="H102" t="n">
-        <v>3.6277</v>
+        <v>3.7959</v>
       </c>
     </row>
     <row r="103">
@@ -3706,20 +3706,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9346</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="F103" t="n">
-        <v>1.5066</v>
+        <v>0.449</v>
       </c>
       <c r="G103" t="n">
-        <v>2.0186</v>
+        <v>1.6743</v>
       </c>
       <c r="H103" t="n">
-        <v>3.6362</v>
+        <v>3.7847</v>
       </c>
     </row>
     <row r="104">
@@ -3738,20 +3738,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9267</v>
+        <v>0.9516</v>
       </c>
       <c r="F104" t="n">
-        <v>1.5057</v>
+        <v>0.4361</v>
       </c>
       <c r="G104" t="n">
-        <v>2.0818</v>
+        <v>1.8747</v>
       </c>
       <c r="H104" t="n">
-        <v>3.6329</v>
+        <v>3.8289</v>
       </c>
     </row>
     <row r="105">
@@ -3770,20 +3770,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9779</v>
+        <v>0.9555</v>
       </c>
       <c r="F105" t="n">
-        <v>1.4918</v>
+        <v>0.447</v>
       </c>
       <c r="G105" t="n">
-        <v>1.354</v>
+        <v>1.7831</v>
       </c>
       <c r="H105" t="n">
-        <v>3.5826</v>
+        <v>3.7916</v>
       </c>
     </row>
     <row r="106">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9272</v>
+        <v>0.9782</v>
       </c>
       <c r="F106" t="n">
-        <v>1.5</v>
+        <v>0.4577</v>
       </c>
       <c r="G106" t="n">
-        <v>2.07</v>
+        <v>1.3751</v>
       </c>
       <c r="H106" t="n">
-        <v>3.6123</v>
+        <v>3.7547</v>
       </c>
     </row>
     <row r="107">
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9794</v>
+        <v>0.9482</v>
       </c>
       <c r="F107" t="n">
-        <v>1.5036</v>
+        <v>0.4489</v>
       </c>
       <c r="G107" t="n">
-        <v>1.3308</v>
+        <v>1.8692</v>
       </c>
       <c r="H107" t="n">
-        <v>3.6253</v>
+        <v>3.7852</v>
       </c>
     </row>
     <row r="108">
@@ -3866,20 +3866,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9606</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="F108" t="n">
-        <v>1.5995</v>
+        <v>0.3787</v>
       </c>
       <c r="G108" t="n">
-        <v>1.8873</v>
+        <v>1.7895</v>
       </c>
       <c r="H108" t="n">
-        <v>3.9555</v>
+        <v>4.019</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9832</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="F109" t="n">
-        <v>1.5604</v>
+        <v>0.4093</v>
       </c>
       <c r="G109" t="n">
-        <v>1.4161</v>
+        <v>1.791</v>
       </c>
       <c r="H109" t="n">
-        <v>3.8245</v>
+        <v>3.9186</v>
       </c>
     </row>
     <row r="110">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9808</v>
+        <v>0.9179</v>
       </c>
       <c r="F110" t="n">
-        <v>1.5246</v>
+        <v>0.4299</v>
       </c>
       <c r="G110" t="n">
-        <v>1.4248</v>
+        <v>2.3101</v>
       </c>
       <c r="H110" t="n">
-        <v>3.7003</v>
+        <v>3.8498</v>
       </c>
     </row>
     <row r="111">
@@ -3962,20 +3962,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9818</v>
+        <v>0.9515</v>
       </c>
       <c r="F111" t="n">
-        <v>1.5119</v>
+        <v>0.4472</v>
       </c>
       <c r="G111" t="n">
-        <v>1.3588</v>
+        <v>1.813</v>
       </c>
       <c r="H111" t="n">
-        <v>3.6552</v>
+        <v>3.7909</v>
       </c>
     </row>
     <row r="112">
@@ -3994,20 +3994,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9607</v>
+        <v>0.9617</v>
       </c>
       <c r="F112" t="n">
-        <v>1.594</v>
+        <v>0.3763</v>
       </c>
       <c r="G112" t="n">
-        <v>1.8924</v>
+        <v>1.7933</v>
       </c>
       <c r="H112" t="n">
-        <v>3.9375</v>
+        <v>4.0267</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9294</v>
+        <v>0.9603</v>
       </c>
       <c r="F113" t="n">
-        <v>1.5531</v>
+        <v>0.4107</v>
       </c>
       <c r="G113" t="n">
-        <v>2.2843</v>
+        <v>1.7918</v>
       </c>
       <c r="H113" t="n">
-        <v>3.7994</v>
+        <v>3.914</v>
       </c>
     </row>
     <row r="114">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9806</v>
+        <v>0.9185</v>
       </c>
       <c r="F114" t="n">
-        <v>1.5261</v>
+        <v>0.4306</v>
       </c>
       <c r="G114" t="n">
-        <v>1.4195</v>
+        <v>2.3101</v>
       </c>
       <c r="H114" t="n">
-        <v>3.7055</v>
+        <v>3.8473</v>
       </c>
     </row>
     <row r="115">
@@ -4090,20 +4090,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="F115" t="n">
-        <v>1.5129</v>
+        <v>0.4427</v>
       </c>
       <c r="G115" t="n">
-        <v>1.3698</v>
+        <v>1.7945</v>
       </c>
       <c r="H115" t="n">
-        <v>3.6589</v>
+        <v>3.8062</v>
       </c>
     </row>
     <row r="116">
@@ -4122,20 +4122,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9679</v>
       </c>
       <c r="F116" t="n">
-        <v>1.5285</v>
+        <v>0.3781</v>
       </c>
       <c r="G116" t="n">
-        <v>1.9068</v>
+        <v>1.5871</v>
       </c>
       <c r="H116" t="n">
-        <v>3.7139</v>
+        <v>4.0208</v>
       </c>
     </row>
     <row r="117">
@@ -4154,20 +4154,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.9702</v>
+        <v>0.9362</v>
       </c>
       <c r="F117" t="n">
-        <v>1.5108</v>
+        <v>0.393</v>
       </c>
       <c r="G117" t="n">
-        <v>1.5354</v>
+        <v>1.9881</v>
       </c>
       <c r="H117" t="n">
-        <v>3.6513</v>
+        <v>3.9725</v>
       </c>
     </row>
     <row r="118">
@@ -4186,20 +4186,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9779</v>
+        <v>0.9555</v>
       </c>
       <c r="F118" t="n">
-        <v>1.4918</v>
+        <v>0.447</v>
       </c>
       <c r="G118" t="n">
-        <v>1.354</v>
+        <v>1.7831</v>
       </c>
       <c r="H118" t="n">
-        <v>3.5826</v>
+        <v>3.7916</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9294</v>
+        <v>0.9603</v>
       </c>
       <c r="F119" t="n">
-        <v>1.5531</v>
+        <v>0.4107</v>
       </c>
       <c r="G119" t="n">
-        <v>2.2843</v>
+        <v>1.7918</v>
       </c>
       <c r="H119" t="n">
-        <v>3.7994</v>
+        <v>3.914</v>
       </c>
     </row>
     <row r="120">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9083</v>
+        <v>0.9507</v>
       </c>
       <c r="F120" t="n">
-        <v>1.6283</v>
+        <v>0.3397</v>
       </c>
       <c r="G120" t="n">
-        <v>2.362</v>
+        <v>1.8733</v>
       </c>
       <c r="H120" t="n">
-        <v>4.0496</v>
+        <v>4.1431</v>
       </c>
     </row>
     <row r="121">
@@ -4282,20 +4282,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9083</v>
+        <v>0.9507</v>
       </c>
       <c r="F121" t="n">
-        <v>1.6283</v>
+        <v>0.3397</v>
       </c>
       <c r="G121" t="n">
-        <v>2.362</v>
+        <v>1.8733</v>
       </c>
       <c r="H121" t="n">
-        <v>4.0496</v>
+        <v>4.1431</v>
       </c>
     </row>
     <row r="122">
@@ -4314,20 +4314,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9774</v>
+        <v>0.9585</v>
       </c>
       <c r="F122" t="n">
-        <v>1.4805</v>
+        <v>0.4495</v>
       </c>
       <c r="G122" t="n">
-        <v>1.336</v>
+        <v>1.6455</v>
       </c>
       <c r="H122" t="n">
-        <v>3.5413</v>
+        <v>3.7832</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9293</v>
+        <v>0.9603</v>
       </c>
       <c r="F123" t="n">
-        <v>1.5533</v>
+        <v>0.4109</v>
       </c>
       <c r="G123" t="n">
-        <v>2.2853</v>
+        <v>1.7914</v>
       </c>
       <c r="H123" t="n">
-        <v>3.8</v>
+        <v>3.9135</v>
       </c>
     </row>
     <row r="124">
@@ -4382,16 +4382,16 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9625</v>
+        <v>0.96</v>
       </c>
       <c r="F124" t="n">
-        <v>1.5373</v>
+        <v>0.4259</v>
       </c>
       <c r="G124" t="n">
-        <v>1.7572</v>
+        <v>1.8236</v>
       </c>
       <c r="H124" t="n">
-        <v>3.7446</v>
+        <v>3.8633</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9575</v>
+        <v>0.9562</v>
       </c>
       <c r="F125" t="n">
-        <v>1.4828</v>
+        <v>0.4582</v>
       </c>
       <c r="G125" t="n">
-        <v>1.6989</v>
+        <v>1.7348</v>
       </c>
       <c r="H125" t="n">
-        <v>3.5499</v>
+        <v>3.7531</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9815</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="F126" t="n">
-        <v>1.6039</v>
+        <v>0.3099</v>
       </c>
       <c r="G126" t="n">
-        <v>1.4671</v>
+        <v>1.823</v>
       </c>
       <c r="H126" t="n">
-        <v>3.97</v>
+        <v>4.2357</v>
       </c>
     </row>
     <row r="127">
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.9574</v>
+        <v>0.9244</v>
       </c>
       <c r="F127" t="n">
-        <v>1.5429</v>
+        <v>0.3962</v>
       </c>
       <c r="G127" t="n">
-        <v>1.7178</v>
+        <v>2.1617</v>
       </c>
       <c r="H127" t="n">
-        <v>3.7643</v>
+        <v>3.9619</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/tlip.MS/RANDOMSEARCH_DETAILS_tlip.MS.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/tlip.MS/RANDOMSEARCH_DETAILS_tlip.MS.xlsx
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -3066,17 +3066,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.8924</v>
+        <v>0.8925</v>
       </c>
       <c r="F83" t="n">
         <v>0.2945</v>
       </c>
       <c r="G83" t="n">
-        <v>2.6372</v>
+        <v>2.6365</v>
       </c>
       <c r="H83" t="n">
         <v>4.2827</v>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -4474,17 +4474,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.9245</v>
+        <v>0.9244</v>
       </c>
       <c r="F127" t="n">
         <v>0.3962</v>
       </c>
       <c r="G127" t="n">
-        <v>2.1608</v>
+        <v>2.1617</v>
       </c>
       <c r="H127" t="n">
         <v>3.9619</v>
